--- a/backend/income_details.xlsx
+++ b/backend/income_details.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,21 +415,77 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Web</v>
+        <v>c</v>
       </c>
       <c r="B2">
-        <v>10000</v>
+        <v>5</v>
       </c>
       <c r="C2" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="D2" t="str">
+        <v>27/3/2026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>d</v>
+      </c>
+      <c r="B3">
+        <v>45</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Food</v>
+      </c>
+      <c r="D3" t="str">
+        <v>27/3/2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Freelance</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="D4" t="str">
+        <v>27/3/2026</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="B5">
+        <v>2000</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="D5" t="str">
+        <v>27/3/2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Web Scraping</v>
+      </c>
+      <c r="B6">
+        <v>50000</v>
+      </c>
+      <c r="C6" t="str">
         <v>Freelancing</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D6" t="str">
         <v>22/3/2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>